--- a/pinyin_audio_tracking.xlsx
+++ b/pinyin_audio_tracking.xlsx
@@ -27444,16 +27444,16 @@
         <v>Success</v>
       </c>
       <c r="F933" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383185/da-phat-am-tieng-trung/audio/lu4.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/lv4.mp3</v>
       </c>
       <c r="G933" t="str">
         <v>Success</v>
       </c>
       <c r="H933" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/lü4.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/lv4.mp3</v>
       </c>
       <c r="I933" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="934">
@@ -27473,16 +27473,16 @@
         <v>Success</v>
       </c>
       <c r="F934" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383185/da-phat-am-tieng-trung/audio/lu1.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/lv1.mp3</v>
       </c>
       <c r="G934" t="str">
         <v>Success</v>
       </c>
       <c r="H934" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/lü1.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/lv1.mp3</v>
       </c>
       <c r="I934" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="935">
@@ -27502,16 +27502,16 @@
         <v>Success</v>
       </c>
       <c r="F935" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383186/da-phat-am-tieng-trung/audio/lu2.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/lv2.mp3</v>
       </c>
       <c r="G935" t="str">
         <v>Success</v>
       </c>
       <c r="H935" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/lü2.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/lv2.mp3</v>
       </c>
       <c r="I935" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="936">
@@ -27531,16 +27531,16 @@
         <v>Success</v>
       </c>
       <c r="F936" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383185/da-phat-am-tieng-trung/audio/lu3.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/lv3.mp3</v>
       </c>
       <c r="G936" t="str">
         <v>Success</v>
       </c>
       <c r="H936" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/lü3.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/lv3.mp3</v>
       </c>
       <c r="I936" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="937">
@@ -27589,16 +27589,16 @@
         <v>Success</v>
       </c>
       <c r="F938" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383188/da-phat-am-tieng-trung/audio/l%C3%BCe4.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/lve4.mp3</v>
       </c>
       <c r="G938" t="str">
         <v>Success</v>
       </c>
       <c r="H938" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/lüe4.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/lve4.mp3</v>
       </c>
       <c r="I938" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="939">
@@ -27618,16 +27618,16 @@
         <v>Success</v>
       </c>
       <c r="F939" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383188/da-phat-am-tieng-trung/audio/l%C3%BCe2.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/lve2.mp3</v>
       </c>
       <c r="G939" t="str">
         <v>Success</v>
       </c>
       <c r="H939" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/lüe2.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/lve2.mp3</v>
       </c>
       <c r="I939" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="940">
@@ -27647,16 +27647,16 @@
         <v>Success</v>
       </c>
       <c r="F940" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383188/da-phat-am-tieng-trung/audio/l%C3%BCe3.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/lve3.mp3</v>
       </c>
       <c r="G940" t="str">
         <v>Success</v>
       </c>
       <c r="H940" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/lüe3.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/lve3.mp3</v>
       </c>
       <c r="I940" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="941">
@@ -27676,16 +27676,16 @@
         <v>Success</v>
       </c>
       <c r="F941" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383188/da-phat-am-tieng-trung/audio/l%C3%BCe1.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/lve1.mp3</v>
       </c>
       <c r="G941" t="str">
         <v>Success</v>
       </c>
       <c r="H941" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/lüe1.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/lve1.mp3</v>
       </c>
       <c r="I941" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="942">
@@ -33679,16 +33679,16 @@
         <v>Success</v>
       </c>
       <c r="F1148" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383252/da-phat-am-tieng-trung/audio/nu1.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/nv1.mp3</v>
       </c>
       <c r="G1148" t="str">
         <v>Success</v>
       </c>
       <c r="H1148" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/nü1.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/nv1.mp3</v>
       </c>
       <c r="I1148" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="1149">
@@ -33708,16 +33708,16 @@
         <v>Success</v>
       </c>
       <c r="F1149" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383252/da-phat-am-tieng-trung/audio/nu4.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/nv4.mp3</v>
       </c>
       <c r="G1149" t="str">
         <v>Success</v>
       </c>
       <c r="H1149" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/nü4.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/nv4.mp3</v>
       </c>
       <c r="I1149" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="1150">
@@ -33737,16 +33737,16 @@
         <v>Success</v>
       </c>
       <c r="F1150" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383252/da-phat-am-tieng-trung/audio/nu2.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/nv2.mp3</v>
       </c>
       <c r="G1150" t="str">
         <v>Success</v>
       </c>
       <c r="H1150" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/nü2.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/nv2.mp3</v>
       </c>
       <c r="I1150" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="1151">
@@ -33766,16 +33766,16 @@
         <v>Success</v>
       </c>
       <c r="F1151" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383252/da-phat-am-tieng-trung/audio/nu3.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/nv3.mp3</v>
       </c>
       <c r="G1151" t="str">
         <v>Success</v>
       </c>
       <c r="H1151" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/nü3.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/nv3.mp3</v>
       </c>
       <c r="I1151" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="1152">
@@ -33824,16 +33824,16 @@
         <v>Success</v>
       </c>
       <c r="F1153" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383254/da-phat-am-tieng-trung/audio/n%C3%BCe2.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/nve2.mp3</v>
       </c>
       <c r="G1153" t="str">
         <v>Success</v>
       </c>
       <c r="H1153" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/nüe2.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/nve2.mp3</v>
       </c>
       <c r="I1153" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="1154">
@@ -33853,16 +33853,16 @@
         <v>Success</v>
       </c>
       <c r="F1154" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383254/da-phat-am-tieng-trung/audio/n%C3%BCe3.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/nve3.mp3</v>
       </c>
       <c r="G1154" t="str">
         <v>Success</v>
       </c>
       <c r="H1154" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/nüe3.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/nve3.mp3</v>
       </c>
       <c r="I1154" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="1155">
@@ -33882,16 +33882,16 @@
         <v>Success</v>
       </c>
       <c r="F1155" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383254/da-phat-am-tieng-trung/audio/n%C3%BCe1.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/nve1.mp3</v>
       </c>
       <c r="G1155" t="str">
         <v>Success</v>
       </c>
       <c r="H1155" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/nüe1.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/nve1.mp3</v>
       </c>
       <c r="I1155" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="1156">
@@ -33911,16 +33911,16 @@
         <v>Success</v>
       </c>
       <c r="F1156" t="str">
-        <v>https://res.cloudinary.com/zopjocdi/video/upload/v1785383254/da-phat-am-tieng-trung/audio/n%C3%BCe4.mp3</v>
+        <v>https://res.cloudinary.com/zopjocdi/video/upload/da-phat-am-tieng-trung/audio/nve4.mp3</v>
       </c>
       <c r="G1156" t="str">
         <v>Success</v>
       </c>
       <c r="H1156" t="str">
-        <v>https://studycli.org/wp-content/uploads/mp3/nüe4.mp3</v>
+        <v>https://studycli.org/wp-content/uploads/mp3/nve4.mp3</v>
       </c>
       <c r="I1156" t="str">
-        <v>Failed (404)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="1157">

--- a/pinyin_audio_tracking.xlsx
+++ b/pinyin_audio_tracking.xlsx
@@ -51175,7 +51175,7 @@
         <v>https://studycli.org/wp-content/uploads/mp3/xing1.mp3</v>
       </c>
       <c r="I1751" t="str">
-        <v>Failed (false)</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="1752">
